--- a/docs/perechen-otchetov/obrazcy/ФО-25.xlsx
+++ b/docs/perechen-otchetov/obrazcy/ФО-25.xlsx
@@ -662,7 +662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L91"/>
+  <dimension ref="A1:L92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -835,10 +835,10 @@
         <v>24</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" s="8" t="n">
         <v>25</v>
@@ -2017,10 +2017,10 @@
         <v>14</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G40" s="12" t="n">
         <v>13</v>
@@ -3189,10 +3189,10 @@
         <v>4</v>
       </c>
       <c r="E72" s="17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F72" s="17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G72" s="17" t="n">
         <v>3</v>
@@ -3367,10 +3367,10 @@
       <c r="C77" s="21" t="n"/>
       <c r="D77" s="22" t="n"/>
       <c r="E77" s="23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F77" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G77" s="23" t="n">
         <v>1</v>
@@ -3394,11 +3394,11 @@
     <row r="78" ht="13" customHeight="1">
       <c r="A78" s="25" t="inlineStr">
         <is>
-          <t>Кредит № 25-3/014 от 05.03.2025, KGS</t>
+          <t>Заявка № 21 от 01.09.2026</t>
         </is>
       </c>
       <c r="B78" s="26" t="n">
-        <v>45721</v>
+        <v>46266</v>
       </c>
       <c r="C78" s="27" t="inlineStr">
         <is>
@@ -3410,10 +3410,10 @@
         <v>1</v>
       </c>
       <c r="F78" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G78" s="29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H78" s="29" t="n">
         <v>0</v>
@@ -3424,17 +3424,13 @@
       <c r="J78" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="K78" s="30" t="n">
-        <v>1100</v>
-      </c>
-      <c r="L78" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" ht="24" customHeight="1">
+      <c r="K78" s="28" t="n"/>
+      <c r="L78" s="28" t="n"/>
+    </row>
+    <row r="79" ht="13" customHeight="1">
       <c r="A79" s="25" t="inlineStr">
         <is>
-          <t>Предмет залога «Нежилое помещение, г. Каракол», договор залога № 25-3/014-З1</t>
+          <t>Кредит № 25-3/014 от 05.03.2025, KGS</t>
         </is>
       </c>
       <c r="B79" s="26" t="n">
@@ -3453,10 +3449,10 @@
         <v>0</v>
       </c>
       <c r="G79" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H79" s="29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I79" s="29" t="n">
         <v>0</v>
@@ -3464,91 +3460,91 @@
       <c r="J79" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="K79" s="28" t="n"/>
-      <c r="L79" s="28" t="n"/>
-    </row>
-    <row r="80" ht="13" customHeight="1">
-      <c r="A80" s="19" t="inlineStr">
+      <c r="K79" s="30" t="n">
+        <v>1100</v>
+      </c>
+      <c r="L79" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" ht="24" customHeight="1">
+      <c r="A80" s="25" t="inlineStr">
+        <is>
+          <t>Предмет залога «Нежилое помещение, г. Каракол», договор залога № 25-3/014-З1</t>
+        </is>
+      </c>
+      <c r="B80" s="26" t="n">
+        <v>45721</v>
+      </c>
+      <c r="C80" s="27" t="inlineStr">
+        <is>
+          <t>правило</t>
+        </is>
+      </c>
+      <c r="D80" s="28" t="n"/>
+      <c r="E80" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F80" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I80" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" s="28" t="n"/>
+      <c r="L80" s="28" t="n"/>
+    </row>
+    <row r="81" ht="13" customHeight="1">
+      <c r="A81" s="19" t="inlineStr">
         <is>
           <t>ОсОО «Нарын-Сүт»</t>
         </is>
       </c>
-      <c r="B80" s="20" t="n"/>
-      <c r="C80" s="21" t="n"/>
-      <c r="D80" s="22" t="n"/>
-      <c r="E80" s="23" t="n">
+      <c r="B81" s="20" t="n"/>
+      <c r="C81" s="21" t="n"/>
+      <c r="D81" s="22" t="n"/>
+      <c r="E81" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="F80" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G80" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H80" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I80" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="J80" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K80" s="24" t="n">
+      <c r="F81" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H81" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J81" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" s="24" t="n">
         <v>2200</v>
       </c>
-      <c r="L80" s="24" t="n">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="81" ht="13" customHeight="1">
-      <c r="A81" s="25" t="inlineStr">
-        <is>
-          <t>Кредит № 23-5/071 от 09.08.2023, KGS</t>
-        </is>
-      </c>
-      <c r="B81" s="26" t="n">
-        <v>45147</v>
-      </c>
-      <c r="C81" s="27" t="inlineStr">
-        <is>
-          <t>правило</t>
-        </is>
-      </c>
-      <c r="D81" s="28" t="n"/>
-      <c r="E81" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="F81" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G81" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="H81" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I81" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K81" s="30" t="n">
-        <v>2200</v>
-      </c>
-      <c r="L81" s="30" t="n">
+      <c r="L81" s="24" t="n">
         <v>551</v>
       </c>
     </row>
     <row r="82" ht="13" customHeight="1">
       <c r="A82" s="25" t="inlineStr">
         <is>
-          <t>Требование к заёмщику, кредит № 23-5/071</t>
+          <t>Кредит № 23-5/071 от 09.08.2023, KGS</t>
         </is>
       </c>
       <c r="B82" s="26" t="n">
-        <v>46107</v>
+        <v>45147</v>
       </c>
       <c r="C82" s="27" t="inlineStr">
         <is>
@@ -3563,337 +3559,377 @@
         <v>0</v>
       </c>
       <c r="G82" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H82" s="29" t="n">
         <v>0</v>
       </c>
       <c r="I82" s="29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J82" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="K82" s="28" t="n"/>
-      <c r="L82" s="28" t="n"/>
+      <c r="K82" s="30" t="n">
+        <v>2200</v>
+      </c>
+      <c r="L82" s="30" t="n">
+        <v>551</v>
+      </c>
     </row>
     <row r="83" ht="13" customHeight="1">
-      <c r="A83" s="10" t="inlineStr">
+      <c r="A83" s="25" t="inlineStr">
+        <is>
+          <t>Требование к заёмщику, кредит № 23-5/071</t>
+        </is>
+      </c>
+      <c r="B83" s="26" t="n">
+        <v>46107</v>
+      </c>
+      <c r="C83" s="27" t="inlineStr">
+        <is>
+          <t>правило</t>
+        </is>
+      </c>
+      <c r="D83" s="28" t="n"/>
+      <c r="E83" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F83" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="J83" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" s="28" t="n"/>
+      <c r="L83" s="28" t="n"/>
+    </row>
+    <row r="84" ht="13" customHeight="1">
+      <c r="A84" s="10" t="inlineStr">
         <is>
           <t>Департамент правового обеспечения</t>
         </is>
       </c>
-      <c r="B83" s="11" t="n"/>
-      <c r="C83" s="10" t="n"/>
-      <c r="D83" s="12" t="n">
+      <c r="B84" s="11" t="n"/>
+      <c r="C84" s="10" t="n"/>
+      <c r="D84" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="E83" s="12" t="n">
+      <c r="E84" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="F83" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G83" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H83" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I83" s="12" t="n">
+      <c r="F84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="J83" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K83" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" ht="13" customHeight="1">
-      <c r="A84" s="14" t="inlineStr">
+      <c r="J84" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K84" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" ht="13" customHeight="1">
+      <c r="A85" s="14" t="inlineStr">
         <is>
           <t>Жээнбекова Н. А.</t>
         </is>
       </c>
-      <c r="B84" s="15" t="n"/>
-      <c r="C84" s="16" t="n"/>
-      <c r="D84" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E84" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F84" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G84" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H84" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I84" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J84" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K84" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L84" s="18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" ht="13" customHeight="1">
-      <c r="A85" s="19" t="inlineStr">
+      <c r="B85" s="15" t="n"/>
+      <c r="C85" s="16" t="n"/>
+      <c r="D85" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F85" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K85" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" s="18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" ht="13" customHeight="1">
+      <c r="A86" s="19" t="inlineStr">
         <is>
           <t>ОАО «Бишкексүт»</t>
         </is>
       </c>
-      <c r="B85" s="20" t="n"/>
-      <c r="C85" s="21" t="n"/>
-      <c r="D85" s="22" t="n"/>
-      <c r="E85" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="F85" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G85" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H85" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I85" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J85" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="K85" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L85" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" ht="24" customHeight="1">
-      <c r="A86" s="25" t="inlineStr">
+      <c r="B86" s="20" t="n"/>
+      <c r="C86" s="21" t="n"/>
+      <c r="D86" s="22" t="n"/>
+      <c r="E86" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F86" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K86" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" ht="24" customHeight="1">
+      <c r="A87" s="25" t="inlineStr">
         <is>
           <t>Объект имущества «Здание молокозавода», № 0016</t>
         </is>
       </c>
-      <c r="B86" s="26" t="n">
+      <c r="B87" s="26" t="n">
         <v>46101</v>
       </c>
-      <c r="C86" s="27" t="inlineStr">
+      <c r="C87" s="27" t="inlineStr">
         <is>
           <t>правило</t>
         </is>
       </c>
-      <c r="D86" s="28" t="n"/>
-      <c r="E86" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="F86" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G86" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H86" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I86" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J86" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="K86" s="28" t="n"/>
-      <c r="L86" s="28" t="n"/>
-    </row>
-    <row r="87" ht="13" customHeight="1">
-      <c r="A87" s="14" t="inlineStr">
+      <c r="D87" s="28" t="n"/>
+      <c r="E87" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F87" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K87" s="28" t="n"/>
+      <c r="L87" s="28" t="n"/>
+    </row>
+    <row r="88" ht="13" customHeight="1">
+      <c r="A88" s="14" t="inlineStr">
         <is>
           <t>Сыдыкова А. Т.</t>
         </is>
       </c>
-      <c r="B87" s="15" t="n"/>
-      <c r="C87" s="16" t="n"/>
-      <c r="D87" s="17" t="n">
+      <c r="B88" s="15" t="n"/>
+      <c r="C88" s="16" t="n"/>
+      <c r="D88" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="E87" s="17" t="n">
+      <c r="E88" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="F87" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G87" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H87" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I87" s="17" t="n">
+      <c r="F88" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="J87" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K87" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L87" s="18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" ht="13" customHeight="1">
-      <c r="A88" s="19" t="inlineStr">
+      <c r="J88" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" s="18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" ht="13" customHeight="1">
+      <c r="A89" s="19" t="inlineStr">
         <is>
           <t>ОсОО «Кербен-Жибек»</t>
         </is>
       </c>
-      <c r="B88" s="20" t="n"/>
-      <c r="C88" s="21" t="n"/>
-      <c r="D88" s="22" t="n"/>
-      <c r="E88" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="F88" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G88" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H88" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I88" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="J88" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K88" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L88" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" ht="35" customHeight="1">
-      <c r="A89" s="25" t="inlineStr">
+      <c r="B89" s="20" t="n"/>
+      <c r="C89" s="21" t="n"/>
+      <c r="D89" s="22" t="n"/>
+      <c r="E89" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F89" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J89" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" ht="35" customHeight="1">
+      <c r="A90" s="25" t="inlineStr">
         <is>
           <t>Требование к заёмщику, кредит № 20-5/118</t>
         </is>
       </c>
-      <c r="B89" s="26" t="n">
+      <c r="B90" s="26" t="n">
         <v>46268</v>
       </c>
-      <c r="C89" s="27" t="inlineStr">
+      <c r="C90" s="27" t="inlineStr">
         <is>
           <t>рука: приём передачи требования (иск)</t>
         </is>
       </c>
-      <c r="D89" s="28" t="n"/>
-      <c r="E89" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="F89" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G89" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H89" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I89" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="J89" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K89" s="28" t="n"/>
-      <c r="L89" s="28" t="n"/>
-    </row>
-    <row r="90" ht="13" customHeight="1">
-      <c r="A90" s="19" t="inlineStr">
+      <c r="D90" s="28" t="n"/>
+      <c r="E90" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F90" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="J90" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" s="28" t="n"/>
+      <c r="L90" s="28" t="n"/>
+    </row>
+    <row r="91" ht="13" customHeight="1">
+      <c r="A91" s="19" t="inlineStr">
         <is>
           <t>ОсОО «Нарын-Агро»</t>
         </is>
       </c>
-      <c r="B90" s="20" t="n"/>
-      <c r="C90" s="21" t="n"/>
-      <c r="D90" s="22" t="n"/>
-      <c r="E90" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="F90" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G90" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H90" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I90" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="J90" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K90" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L90" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" ht="35" customHeight="1">
-      <c r="A91" s="25" t="inlineStr">
+      <c r="B91" s="20" t="n"/>
+      <c r="C91" s="21" t="n"/>
+      <c r="D91" s="22" t="n"/>
+      <c r="E91" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F91" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J91" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" ht="35" customHeight="1">
+      <c r="A92" s="25" t="inlineStr">
         <is>
           <t>Требование к заёмщику, кредит № 21-2/077</t>
         </is>
       </c>
-      <c r="B91" s="26" t="n">
+      <c r="B92" s="26" t="n">
         <v>46097</v>
       </c>
-      <c r="C91" s="27" t="inlineStr">
+      <c r="C92" s="27" t="inlineStr">
         <is>
           <t>рука: приём передачи требования (иск)</t>
         </is>
       </c>
-      <c r="D91" s="28" t="n"/>
-      <c r="E91" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="F91" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G91" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H91" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I91" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="J91" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K91" s="28" t="n"/>
-      <c r="L91" s="28" t="n"/>
+      <c r="D92" s="28" t="n"/>
+      <c r="E92" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F92" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="J92" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" s="28" t="n"/>
+      <c r="L92" s="28" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -4768,7 +4804,7 @@
       </c>
       <c r="B36" s="46" t="inlineStr">
         <is>
-          <t>На 01.10.2026 (данные на конец 30.09.2026): ИТОГО — 24 заёмщика, объектов в работе 47: заявок 0, кредитов 25, предметов залога 7, требований 14, имущества 1; остаток основного долга 75 037,500 тыс. сом = ФО-02 (67 729,500) + КЗ-25 (7 308,000) = остаток на конец ФО-24 за сентябрь; просроченная задолженность 10 347,215 = ФО-01 на 01.10.2026.</t>
+          <t>На 01.10.2026 (данные на конец 30.09.2026): ИТОГО — 24 заёмщика, объектов в работе 48: заявок 1, кредитов 25, предметов залога 7, требований 14, имущества 1; остаток основного долга 75 037,500 тыс. сом = ФО-02 «по основной сумме» на 01.10.2026 = остаток на конец ФО-24 за сентябрь; просроченная задолженность 10 347,215 = ФО-01 на 01.10.2026.</t>
         </is>
       </c>
     </row>
@@ -4780,7 +4816,7 @@
       </c>
       <c r="B37" s="46" t="inlineStr">
         <is>
-          <t>Кураторы: Асанов А. К. — 6 заёмщиков, 9 кредитов, 7 требований, остаток 29 822,000, просрочка 4 326,440 (= ФО-01 по Департаменту администрирования кредитов); Бекова Н. С. — 3 заёмщика, 3 кредита (КЗ-11, 25, 26), 12 120,500; Жумабаев Р. С. — 5 заёмщиков, 5 кредитов, 3 требования, 7 470,000, просрочка 1 967,400; Осмонов Б. Т. — 5 заёмщиков, 5 кредитов, 5 предметов залога (КЗ-04, КЗ-14), 1 требование, 18 425,000, просрочка 3 502,375; Токтогулова Г. А. — 4 заёмщика, 3 кредита, 2 предмета (КЗ-18, КЗ-20), 1 требование, 7 200,000, просрочка 551,000; Сыдыкова А. Т. — требования КЗ-05 и КЗ-23; Жээнбекова Н. А. — объект имущества КЗ-16.</t>
+          <t>Кураторы: Асанов А. К. — 6 заёмщиков, 9 кредитов, 7 требований, остаток 29 822,000, просрочка 4 326,440 (= ФО-01 по Департаменту администрирования кредитов); Бекова Н. С. — 3 заёмщика, 3 кредита (КЗ-11, 25, 26), 12 120,500; Жумабаев Р. С. — 5 заёмщиков, 5 кредитов, 3 требования, 7 470,000, просрочка 1 967,400; Осмонов Б. Т. — 5 заёмщиков, 5 кредитов, 5 предметов залога (КЗ-04, КЗ-14), 1 требование, 18 425,000, просрочка 3 502,375; Токтогулова Г. А. — 4 заёмщика, 1 заявка (КЗ-20), 3 кредита, 2 предмета (КЗ-18, КЗ-20), 1 требование, 7 200,000, просрочка 551,000; Сыдыкова А. Т. — требования КЗ-05 и КЗ-23; Жээнбекова Н. А. — объект имущества КЗ-16.</t>
         </is>
       </c>
     </row>
@@ -4796,7 +4832,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="105" customHeight="1">
+    <row r="39" ht="135" customHeight="1">
       <c r="A39" s="45" t="inlineStr">
         <is>
           <t>4.</t>
@@ -4804,11 +4840,11 @@
       </c>
       <c r="B39" s="46" t="inlineStr">
         <is>
-          <t>Не входят: кредиты КЗ-08 (списан 17.09.2026, взыскание после списания не ведётся), КЗ-15 (погашен 18.09.2026, запреты сняты 22 и 24.09.2026), КЗ-16 (погашен имуществом 20.03.2026), КЗ-18 (расторгнут 10.09.2026), ОсОО «Эко-Продукт» — долг переведён 09.09.2026, кредит № 21-6/144 стоит под ОсОО «Ысык-Көл Логистик»; заявка КЗ-17 (кредит выдан) и предложение имущества КЗ-16 (решение вынесено). Входят: предмет залога КЗ-18 — запрет не снят, подлежит снятию с 10.09.2026; трактор КЗ-14 — утрачен 12.09.2026, из договора не исключён; объект имущества КЗ-16 — продан в рассрочку, с учёта не снят.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="75" customHeight="1">
+          <t>Не входят: кредиты КЗ-08 (списан 17.09.2026, взыскание после списания не ведётся), КЗ-15 (погашен 18.09.2026, запреты сняты 22 и 24.09.2026), КЗ-16 (погашен имуществом 20.03.2026), КЗ-18 (расторгнут 10.09.2026), ОсОО «Эко-Продукт» — долг переведён 09.09.2026, кредит № 21-6/144 стоит под ОсОО «Ысык-Көл Логистик»; заявки КЗ-11 № 17 (отклонена комиссией 27.08.2026), КЗ-17 № 14, КЗ-18 № 11 и КЗ-26 № 16 (по ним оформлены кредиты) и предложение имущества КЗ-16 (решение вынесено). Входят: индивидуальная заявка КЗ-20 № 21 от 01.09.2026 — на 30.09.2026 «На рассмотрении» в комиссии, решения нет; предмет залога КЗ-18 — запрет не снят, подлежит снятию с 10.09.2026; трактор КЗ-14 — утрачен 12.09.2026, из договора не исключён; объект имущества КЗ-16 — продан в рассрочку, с учёта не снят.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="105" customHeight="1">
       <c r="A40" s="45" t="inlineStr">
         <is>
           <t>5.</t>
@@ -4816,7 +4852,7 @@
       </c>
       <c r="B40" s="46" t="inlineStr">
         <is>
-          <t>Закреплено с: кредит — день договора (КЗ-17 — 08.09.2026, КЗ-26 — 20.08.2026), предмет — день договора залога, требование к заёмщику — первый день просрочки (КЗ-02 — 12.09.2026, КЗ-24 — 01.09.2026), к поручителю — день требования поручителю (КЗ-03 — 24.08.2026), требования, переданные в Департамент правового обеспечения, — день передачи (КЗ-05 — 16.03.2026, КЗ-23 — 03.09.2026), объект имущества — переход права 20.03.2026.</t>
+          <t>Закреплено с: заявка — день регистрации (КЗ-20 — 01.09.2026), кредит — день договора (КЗ-17 — 08.09.2026, КЗ-26 — 20.08.2026; КЗ-07 — 02.06.2021: перевод долга 09.09.2026 на ОсОО «Ысык-Көл Логистик» сменил заёмщика, не куратора), предмет — день договора залога, требование к заёмщику — первый день просрочки (КЗ-02 — 12.09.2026, КЗ-24 — 01.09.2026), к поручителю — день требования поручителю (КЗ-03 — 24.08.2026), требования, переданные в Департамент правового обеспечения, — день передачи (КЗ-05 — 16.03.2026, КЗ-23 — 03.09.2026), объект имущества — переход права 20.03.2026.</t>
         </is>
       </c>
     </row>
@@ -4840,7 +4876,7 @@
       </c>
       <c r="B42" s="46" t="inlineStr">
         <is>
-          <t>Строка разреза = сумма строк на уровень ниже по счётчикам объектов и суммам; «Заёмщиков» не складывается. Отбор «роль: куратор кредита» даёт 25 кредитов и те же суммы; «источник: рука» — 2 требования у Сыдыковой А. Т.</t>
+          <t>Строка разреза = сумма строк на уровень ниже по счётчикам объектов и суммам; «Заёмщиков» не складывается. Отбор «роль: куратор кредита» даёт 25 кредитов и те же суммы; «роль: специалист заявки» — 1 заявку КЗ-20 у Токтогуловой Г. А.; «источник: рука» — 2 требования у Сыдыковой А. Т.</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4888,7 @@
       </c>
       <c r="B43" s="46" t="inlineStr">
         <is>
-          <t>Кураторы кредитов совпадают с ФО-08, ФО-18 и ФО-20: Бекова Н. С. — КЗ-26, Осмонов Б. Т. — КЗ-12 и КЗ-14, Токтогулова Г. А. — КЗ-20; задания по залогу КЗ-14 и КЗ-20 в ФО-20 — у кураторов залога этого отчёта.</t>
+          <t>Кураторы кредитов совпадают с ФО-08 (Бекова Н. С. — КЗ-26, Осмонов Б. Т. — КЗ-12), ФО-18 и ФО-20 (Осмонов Б. Т. — КЗ-14, Токтогулова Г. А. — КЗ-20); задания по залогу КЗ-14 и КЗ-20 в ФО-20 — у кураторов залога этого отчёта.</t>
         </is>
       </c>
     </row>
